--- a/Network/jelszavak.xlsx
+++ b/Network/jelszavak.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github Repo\final-project-2025-26\Network\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E885573-330D-48F1-8DCB-CDB66403F9C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD5F29CC-A64F-49DA-82B3-5B7C59A896AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -367,7 +367,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">

--- a/Network/jelszavak.xlsx
+++ b/Network/jelszavak.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github Repo\final-project-2025-26\Network\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD5F29CC-A64F-49DA-82B3-5B7C59A896AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFA486EB-6A9B-4AA4-8E36-91E50A979D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="78">
   <si>
     <t>SSID</t>
   </si>
@@ -254,6 +254,12 @@
   </si>
   <si>
     <t>SSH VLAN2</t>
+  </si>
+  <si>
+    <t>ASA</t>
+  </si>
+  <si>
+    <t>ASAPass0</t>
   </si>
 </sst>
 </file>
@@ -310,7 +316,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -333,42 +339,17 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -707,7 +688,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE3D53F7-C2EF-4C5A-ACDE-312F4090DEFA}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" customWidth="1"/>
@@ -721,22 +702,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>36</v>
       </c>
       <c r="G1" s="5" t="s">
@@ -885,77 +866,67 @@
       <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
+      <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>43</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>67</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>43</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -963,24 +934,50 @@
         <v>43</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H12" s="4" t="s">
         <v>69</v>
       </c>
     </row>

--- a/Network/jelszavak.xlsx
+++ b/Network/jelszavak.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github Repo\final-project-2025-26\Network\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFA486EB-6A9B-4AA4-8E36-91E50A979D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B606932-1052-4711-986D-AE1BED6CF0A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Network/jelszavak.xlsx
+++ b/Network/jelszavak.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github Repo\final-project-2025-26\Network\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B606932-1052-4711-986D-AE1BED6CF0A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B1A6A57-7805-4401-BE77-7B3FCEDCB2E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
